--- a/r/astr/test_astr_alignt_columns.xlsx
+++ b/r/astr/test_astr_alignt_columns.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TH282424\Rprojects\iramat-dev\r\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TH282424\Rprojects\iramat-dev\r\astr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1C9837-C964-4AC2-83C3-CB0F5A416FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9640AC94-9BF3-4438-880C-578FFE8E3CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="29016" windowHeight="15696" xr2:uid="{D929D80D-281F-4210-AA08-8E8B61D54EE3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D929D80D-281F-4210-AA08-8E8B61D54EE3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
